--- a/SGC-CKN/Excel/c146f2e6-6636-4973-bbec-955b76a4bc31_Thanh_Hoá_P11-64_D800_04-04-2026.xlsx
+++ b/SGC-CKN/Excel/c146f2e6-6636-4973-bbec-955b76a4bc31_Thanh_Hoá_P11-64_D800_04-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="65">
   <si>
     <t>Dự án</t>
   </si>
@@ -53,7 +53,7 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>22:30 03/04/2026</t>
+    <t>19:45 03/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
@@ -92,7 +92,10 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>Đất lấp</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Sét pha, xám nâu, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">19:45
@@ -109,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">20:20
@@ -119,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">22:30
@@ -133,11 +136,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23:20
-04/04/2026</t>
+    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">01:30
@@ -147,7 +146,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
   </si>
   <si>
     <t xml:space="preserve">02:00
@@ -157,7 +156,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
+    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">02:20
@@ -167,33 +166,23 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">03:15
 04/04/2026</t>
   </si>
   <si>
+    <t>Chạm sỏi 44,9 m</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">05:17
-04/04/2026</t>
-  </si>
-  <si>
-    <t>Chạm sỏi 44,9 m</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
 04/04/2026</t>
   </si>
   <si>
@@ -234,7 +223,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -305,17 +294,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF831843"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -328,7 +306,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,17 +345,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFECACA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -398,16 +376,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBCFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -503,7 +471,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -538,26 +506,26 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -595,25 +563,13 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -639,7 +595,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8096250" cy="10477500"/>
@@ -999,7 +955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1190,136 +1146,136 @@
         <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-0.96</v>
+        <v>-2.06</v>
       </c>
       <c r="H11" s="5">
         <v>0.08</v>
       </c>
       <c r="I11" s="5">
-        <v>0.96</v>
+        <v>2.06</v>
       </c>
       <c r="J11" s="8">
-        <v>11.52</v>
+        <v>24.72</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-0.96</v>
+        <v>-2.06</v>
       </c>
       <c r="G12" s="9">
-        <v>-2.06</v>
+        <v>-12.26</v>
       </c>
       <c r="H12" s="9">
         <v>0.5</v>
       </c>
       <c r="I12" s="9">
-        <v>1.1</v>
-      </c>
-      <c r="J12" s="12">
-        <v>2.2</v>
+        <v>10.2</v>
+      </c>
+      <c r="J12" s="8">
+        <v>20.4</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="13" t="s">
+      <c r="A13" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="15" t="s">
+      <c r="C13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="13">
-        <v>-2.06</v>
-      </c>
-      <c r="G13" s="13">
+      <c r="E13" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="12">
         <v>-12.26</v>
       </c>
-      <c r="H13" s="13">
+      <c r="G13" s="12">
+        <v>-17.46</v>
+      </c>
+      <c r="H13" s="12">
         <v>0.5</v>
       </c>
-      <c r="I13" s="13">
-        <v>10.2</v>
+      <c r="I13" s="12">
+        <v>5.2</v>
       </c>
       <c r="J13" s="8">
-        <v>20.4</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>29</v>
+        <v>10.4</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="16">
-        <v>-12.26</v>
-      </c>
-      <c r="G14" s="16">
+      <c r="F14" s="15">
         <v>-17.46</v>
       </c>
-      <c r="H14" s="16">
-        <v>2.17</v>
-      </c>
-      <c r="I14" s="16">
-        <v>5.2</v>
-      </c>
-      <c r="J14" s="12">
-        <v>2.4</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>29</v>
+      <c r="G14" s="15">
+        <v>-28.16</v>
+      </c>
+      <c r="H14" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="I14" s="15">
+        <v>10.7</v>
+      </c>
+      <c r="J14" s="18">
+        <v>4.28</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1339,22 +1295,22 @@
         <v>43</v>
       </c>
       <c r="F15" s="19">
-        <v>-17.46</v>
+        <v>-28.16</v>
       </c>
       <c r="G15" s="19">
-        <v>-28.16</v>
+        <v>-34.96</v>
       </c>
       <c r="H15" s="19">
         <v>0.5</v>
       </c>
       <c r="I15" s="19">
-        <v>10.7</v>
+        <v>6.8</v>
       </c>
       <c r="J15" s="8">
-        <v>21.4</v>
+        <v>13.6</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1374,22 +1330,22 @@
         <v>46</v>
       </c>
       <c r="F16" s="22">
-        <v>-28.16</v>
+        <v>-34.96</v>
       </c>
       <c r="G16" s="22">
-        <v>-34.96</v>
+        <v>-37.46</v>
       </c>
       <c r="H16" s="22">
         <v>0.33</v>
       </c>
       <c r="I16" s="22">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="J16" s="8">
-        <v>20.4</v>
+        <v>7.5</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1409,109 +1365,75 @@
         <v>49</v>
       </c>
       <c r="F17" s="25">
-        <v>-34.96</v>
+        <v>-37.46</v>
       </c>
       <c r="G17" s="25">
-        <v>-37.46</v>
+        <v>-44.9</v>
       </c>
       <c r="H17" s="25">
         <v>0.92</v>
       </c>
       <c r="I17" s="25">
-        <v>2.5</v>
-      </c>
-      <c r="J17" s="12">
-        <v>2.73</v>
+        <v>7.44</v>
+      </c>
+      <c r="J17" s="8">
+        <v>8.12</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" s="30" t="s">
         <v>49</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="28">
-        <v>-37.46</v>
+        <v>-44.9</v>
       </c>
       <c r="G18" s="28">
-        <v>-44.9</v>
+        <v>-49.6</v>
       </c>
       <c r="H18" s="28">
         <v>2.03</v>
       </c>
       <c r="I18" s="28">
-        <v>7.44</v>
-      </c>
-      <c r="J18" s="12">
-        <v>3.66</v>
+        <v>4.7</v>
+      </c>
+      <c r="J18" s="18">
+        <v>2.31</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="32" t="s">
+    </row>
+    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="31">
-        <v>-44.9</v>
-      </c>
-      <c r="G19" s="31">
-        <v>-49.6</v>
-      </c>
-      <c r="H19" s="31">
-        <v>18.72</v>
-      </c>
-      <c r="I19" s="31">
-        <v>4.7</v>
-      </c>
-      <c r="J19" s="34">
-        <v>0.25</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-    </row>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1571,7 +1493,6 @@
     <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
@@ -1582,7 +1503,7 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A21:K21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1592,7 +1513,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1605,31 +1526,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1640,7 +1561,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
@@ -1649,16 +1570,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-0.96</v>
+        <v>-2.06</v>
       </c>
       <c r="G2" s="5">
         <v>0.08</v>
       </c>
       <c r="H2" s="5">
-        <v>0.96</v>
+        <v>2.06</v>
       </c>
       <c r="I2" s="8">
-        <v>11.52</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1669,83 +1590,83 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-0.96</v>
+        <v>-2.06</v>
       </c>
       <c r="F3" s="9">
-        <v>-2.06</v>
+        <v>-12.26</v>
       </c>
       <c r="G3" s="9">
         <v>0.5</v>
       </c>
       <c r="H3" s="9">
-        <v>1.1</v>
-      </c>
-      <c r="I3" s="12">
-        <v>2.2</v>
+        <v>10.2</v>
+      </c>
+      <c r="I3" s="8">
+        <v>20.4</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="13">
+      <c r="C4" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
-        <v>-2.06</v>
-      </c>
-      <c r="F4" s="13">
+      <c r="E4" s="12">
         <v>-12.26</v>
       </c>
-      <c r="G4" s="13">
+      <c r="F4" s="12">
+        <v>-17.46</v>
+      </c>
+      <c r="G4" s="12">
         <v>0.5</v>
       </c>
-      <c r="H4" s="13">
-        <v>10.2</v>
+      <c r="H4" s="12">
+        <v>5.2</v>
       </c>
       <c r="I4" s="8">
-        <v>20.4</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="16">
+      <c r="C5" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
-        <v>-12.26</v>
-      </c>
-      <c r="F5" s="16">
+      <c r="E5" s="15">
         <v>-17.46</v>
       </c>
-      <c r="G5" s="16">
-        <v>2.17</v>
-      </c>
-      <c r="H5" s="16">
-        <v>5.2</v>
-      </c>
-      <c r="I5" s="12">
-        <v>2.4</v>
+      <c r="F5" s="15">
+        <v>-28.16</v>
+      </c>
+      <c r="G5" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="H5" s="15">
+        <v>10.7</v>
+      </c>
+      <c r="I5" s="18">
+        <v>4.28</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1762,19 +1683,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-17.46</v>
+        <v>-28.16</v>
       </c>
       <c r="F6" s="19">
-        <v>-28.16</v>
+        <v>-34.96</v>
       </c>
       <c r="G6" s="19">
         <v>0.5</v>
       </c>
       <c r="H6" s="19">
-        <v>10.7</v>
+        <v>6.8</v>
       </c>
       <c r="I6" s="8">
-        <v>21.4</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1791,19 +1712,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-28.16</v>
+        <v>-34.96</v>
       </c>
       <c r="F7" s="22">
-        <v>-34.96</v>
+        <v>-37.46</v>
       </c>
       <c r="G7" s="22">
         <v>0.33</v>
       </c>
       <c r="H7" s="22">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="I7" s="8">
-        <v>20.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1820,19 +1741,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-34.96</v>
+        <v>-37.46</v>
       </c>
       <c r="F8" s="25">
-        <v>-37.46</v>
+        <v>-44.9</v>
       </c>
       <c r="G8" s="25">
         <v>0.92</v>
       </c>
       <c r="H8" s="25">
-        <v>2.5</v>
-      </c>
-      <c r="I8" s="12">
-        <v>2.73</v>
+        <v>7.44</v>
+      </c>
+      <c r="I8" s="8">
+        <v>8.12</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1843,83 +1764,54 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-37.46</v>
+        <v>-44.9</v>
       </c>
       <c r="F9" s="28">
-        <v>-44.9</v>
+        <v>-49.6</v>
       </c>
       <c r="G9" s="28">
         <v>2.03</v>
       </c>
       <c r="H9" s="28">
-        <v>7.44</v>
-      </c>
-      <c r="I9" s="12">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="31">
-        <v>9</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="31">
-        <v>1</v>
-      </c>
-      <c r="E10" s="31">
-        <v>-44.9</v>
-      </c>
-      <c r="F10" s="31">
+        <v>4.7</v>
+      </c>
+      <c r="I9" s="18">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="33">
+        <v>8</v>
+      </c>
+      <c r="E10" s="33">
+        <v>0</v>
+      </c>
+      <c r="F10" s="33">
         <v>-49.6</v>
       </c>
-      <c r="G10" s="31">
-        <v>18.72</v>
-      </c>
-      <c r="H10" s="31">
-        <v>4.7</v>
-      </c>
-      <c r="I10" s="34">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="37">
-        <v>9</v>
-      </c>
-      <c r="E11" s="37">
-        <v>0</v>
-      </c>
-      <c r="F11" s="37">
-        <v>-49.6</v>
-      </c>
-      <c r="G11" s="37">
-        <v>25.75</v>
-      </c>
-      <c r="H11" s="37">
+      <c r="G10" s="33">
+        <v>7.37</v>
+      </c>
+      <c r="H10" s="33">
         <v>49.6</v>
       </c>
-      <c r="I11" s="37">
-        <v>1.93</v>
+      <c r="I10" s="33">
+        <v>6.73</v>
       </c>
     </row>
   </sheetData>
